--- a/Input/Gilead_Sample_03_16.xlsx
+++ b/Input/Gilead_Sample_03_16.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://procdna-my.sharepoint.com/personal/tanish_jain_procdna_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://procdna-my.sharepoint.com/personal/aviral_saxena_procdna_com/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B24DF6A-1DF9-4C26-8F68-A6088B850EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{9D4DBD42-0D54-4984-8994-8D00513A47E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515C5765-F25E-49C2-AEF9-052C291FF89A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{975F87C7-CDE5-4775-9D31-4F67F17AFF7D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{975F87C7-CDE5-4775-9D31-4F67F17AFF7D}"/>
   </bookViews>
   <sheets>
     <sheet name="IQVIA-OneKey" sheetId="1" r:id="rId1"/>
-    <sheet name="DCR" sheetId="10" r:id="rId2"/>
-    <sheet name="IQVIA-DDD" sheetId="4" r:id="rId3"/>
-    <sheet name="Alignment" sheetId="3" r:id="rId4"/>
-    <sheet name="Exponent" sheetId="5" r:id="rId5"/>
+    <sheet name="Xponent" sheetId="4" r:id="rId2"/>
+    <sheet name="Alignment" sheetId="3" r:id="rId3"/>
+    <sheet name="IQVIA-DDD" sheetId="5" r:id="rId4"/>
+    <sheet name="DCR" sheetId="10" r:id="rId5"/>
     <sheet name="867_Shipment" sheetId="6" r:id="rId6"/>
     <sheet name="CRM" sheetId="7" r:id="rId7"/>
     <sheet name="Marketing Opt" sheetId="8" r:id="rId8"/>
-    <sheet name="Sales_Credit_Flag" sheetId="9" r:id="rId9"/>
-    <sheet name="Business_Rules" sheetId="11" r:id="rId10"/>
+    <sheet name="Business_Rules" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="157">
   <si>
     <t>HCP_ID</t>
   </si>
@@ -312,9 +311,6 @@
   </si>
   <si>
     <t>Sunlenca</t>
-  </si>
-  <si>
-    <t>Mar</t>
   </si>
   <si>
     <t>SFO-09</t>
@@ -510,12 +506,45 @@
   <si>
     <t>Sales credit for HIV treatment products should only be assigned to HCPs whose specialties are approved in the crediting policy.</t>
   </si>
+  <si>
+    <t>HCO_5551</t>
+  </si>
+  <si>
+    <t>HCO_3332</t>
+  </si>
+  <si>
+    <t>BR-005</t>
+  </si>
+  <si>
+    <t>Infusion to DDD Lag</t>
+  </si>
+  <si>
+    <t>There is typically a 4–6 week lag between the infusion date and when it appears in DDD</t>
+  </si>
+  <si>
+    <t>HCO_9103</t>
+  </si>
+  <si>
+    <t>HCO_8895</t>
+  </si>
+  <si>
+    <t>HCO_7789</t>
+  </si>
+  <si>
+    <t>Green Practice</t>
+  </si>
+  <si>
+    <t>UT South Clinic</t>
+  </si>
+  <si>
+    <t>Boston Associates</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,16 +560,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -550,136 +599,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right style="hair">
-        <color auto="1"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -687,63 +616,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,567 +993,612 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9742014F-4F17-4F61-B591-1E0562DB5901}">
-  <dimension ref="B2:U9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:X21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="U2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="V2" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="2:21">
-      <c r="B3" s="3" t="s">
+      <c r="W2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>1847203944</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="9">
+        <v>44</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="4">
         <v>75206</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="4">
         <v>75206</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="2:21">
-      <c r="B4" s="3" t="s">
+      <c r="W3" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>1847203944</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="9">
+        <v>44</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="4">
         <v>75390</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="4">
         <v>75390</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="U4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="V4" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="2:21">
-      <c r="B5" s="3" t="s">
+      <c r="W4" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>1586047293</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="9">
+        <v>44</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="4">
         <v>2114</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="4">
         <v>2114</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="S5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="T5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="U5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="7" t="s">
+      <c r="V5" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="2:21">
-      <c r="B6" s="3" t="s">
+      <c r="W5" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>1748203957</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="9">
+        <v>44</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="4">
         <v>10027</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="Q6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="4">
         <v>10027</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="S6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="S6" s="7" t="s">
+      <c r="T6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="U6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U6" s="7" t="s">
+      <c r="V6" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="2:21">
-      <c r="B7" s="3" t="s">
+      <c r="W6" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>1639482011</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="9">
+        <v>45</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="4">
         <v>10027</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="O7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="Q7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="4">
         <v>10027</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="S7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="T7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="7" t="s">
+      <c r="U7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U7" s="7" t="s">
+      <c r="V7" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="2:21">
-      <c r="B8" s="3" t="s">
+      <c r="W7" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>1847203948</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="9">
+        <v>44</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="4">
         <v>94103</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="4">
         <v>94103</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="T8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="T8" s="7" t="s">
+      <c r="U8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U8" s="7" t="s">
+      <c r="V8" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="2:21">
-      <c r="B9" s="3" t="s">
+      <c r="W8" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>1739482015</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="9">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="4">
         <v>94103</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="Q9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="4">
         <v>94103</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="S9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="T9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="U9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="V9" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4039378A-6000-4BDB-B998-8418FFE95BFD}">
-  <dimension ref="B2:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="148.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="39" customHeight="1">
-      <c r="B3" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="D5" s="5"/>
+      <c r="W9" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="19:22" x14ac:dyDescent="0.3">
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="19:22" x14ac:dyDescent="0.3">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="19:22" x14ac:dyDescent="0.3">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+    </row>
+    <row r="21" spans="19:22" x14ac:dyDescent="0.3">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1648,67 +1606,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9642E67-F583-4387-AEEE-929FBE41DD09}">
-  <dimension ref="B2:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9EEC87-989E-4C63-A670-8B2EE5D57D7B}">
+  <dimension ref="B2:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
-      <c r="B2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4">
-        <v>46068</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>1847203944</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
+      <c r="D3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="4">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
-        <v>46081</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>1847203944</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="4">
+        <v>1847203944</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="4">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="4">
+        <v>1920483210</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>77</v>
+      <c r="D6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="4">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="4">
+        <v>1920483210</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="4">
+        <v>13</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1717,156 +1744,141 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9EEC87-989E-4C63-A670-8B2EE5D57D7B}">
-  <dimension ref="B2:G8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267ACA7A-0719-4380-B1F9-21DD4DC579B3}">
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7">
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="2" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="2:7">
-      <c r="B3" s="3">
-        <v>1847203944</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="3">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="D2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="4">
+        <v>75206</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3">
-        <v>1847203944</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="3">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="3">
-        <v>1847203944</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="3">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="4">
+        <v>75390</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="3">
-        <v>1847203948</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="4">
+        <v>94103</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="3">
-        <v>15</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="4">
+        <v>10027</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="4">
+        <v>2114</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3">
-        <v>1920483210</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" s="3">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3">
-        <v>1920483210</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="3">
-        <v>13</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>91</v>
+      <c r="D7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="5">
+        <v>94103</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
+        <v>94158</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="5">
+        <v>94107</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1875,141 +1887,117 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267ACA7A-0719-4380-B1F9-21DD4DC579B3}">
-  <dimension ref="B2:E10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B268F00-A4B2-4855-8D0D-89713455565C}">
+  <dimension ref="B2:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
-      <c r="B2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5">
-      <c r="B3" s="3">
-        <v>75206</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="4">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="6">
+        <v>20</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" s="3">
-        <v>75390</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="6">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="3">
-        <v>94103</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="3">
-        <v>10027</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="3">
-        <v>2114</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="1">
-        <v>94103</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="1">
-        <v>94158</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="1">
-        <v>94107</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>99</v>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="6">
+        <v>50</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2018,57 +2006,67 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B268F00-A4B2-4855-8D0D-89713455565C}">
-  <dimension ref="C2:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9642E67-F583-4387-AEEE-929FBE41DD09}">
+  <dimension ref="B2:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8">
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="3:8">
-      <c r="C3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G3" s="3">
-        <v>41</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>100</v>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="13">
+        <v>46068</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="13">
+        <v>46081</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2078,156 +2076,203 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54CE2C2-CFE5-4B51-A210-A229855A0E31}">
-  <dimension ref="B2:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A2:L18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="14">
+        <v>46071</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="9">
+        <v>30</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" s="18">
-        <v>46071</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="9">
+        <v>94103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="14">
+        <v>46044</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="9">
+        <v>60</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="9">
+        <v>10027</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="13">
+        <v>46065</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="7">
-        <v>30</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="4">
+        <v>94107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="13">
+        <v>46073</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="4">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="4">
+        <v>94158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="B7" s="13">
+        <v>46078</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="4">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H7" s="4">
         <v>94103</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="18">
-        <v>46044</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="7">
-        <v>60</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="7">
-        <v>10027</v>
-      </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="4">
-        <v>46065</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="3">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H5" s="3">
-        <v>94107</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="4">
-        <v>46073</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="3">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="3">
-        <v>94158</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="4">
-        <v>46078</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="3">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="3">
-        <v>94103</v>
-      </c>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E13" s="8"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2237,61 +2282,61 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F8F88F-B1C7-48CB-84A4-3368B0D89A0C}">
   <dimension ref="B2:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="2" t="s">
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="13">
+        <v>46067</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46067</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2303,54 +2348,54 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2DB1E1-927D-4BC9-AFE3-B509F21E56D8}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="2" t="s">
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="14">
+        <v>46081</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="3" spans="2:7">
-      <c r="B3" s="18">
-        <v>46081</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2359,70 +2404,58 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7548AA88-DA8C-4132-AC0B-37A1393A1974}">
-  <dimension ref="B2:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4039378A-6000-4BDB-B998-8418FFE95BFD}">
+  <dimension ref="B2:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="148.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
-      <c r="B2" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5">
-      <c r="B3" s="7">
-        <v>44</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="7" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" s="7">
-        <v>11</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="7">
-        <v>45</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>54</v>
+      <c r="C2" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
